--- a/data/trans_camb/PCS12_SP_R2-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/PCS12_SP_R2-Estudios-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población por debajo de la mediana de la puntuación del componente de salud física (SF12)</t>
+          <t>Población por debajo de la mediana (54.994) de la puntuación del componente de salud física (SF12)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 6,89</t>
+          <t>-1,94; 6,65</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,82; 3,71</t>
+          <t>-5,76; 3,88</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,37; 10,87</t>
+          <t>0,5; 10,63</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,66; 1,17</t>
+          <t>-5,23; 1,49</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,02; 0,73</t>
+          <t>-6,67; 0,61</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,95; 7,68</t>
+          <t>0,44; 7,39</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 2,63</t>
+          <t>-2,81; 2,76</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-5,08; 0,73</t>
+          <t>-4,98; 0,59</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,2; 7,99</t>
+          <t>1,96; 7,84</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 11,46</t>
+          <t>-3,01; 11,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-8,85; 6,25</t>
+          <t>-8,81; 6,44</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,62; 18,11</t>
+          <t>0,8; 17,72</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-7,34; 1,6</t>
+          <t>-6,82; 2,01</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-9,09; 1,0</t>
+          <t>-8,75; 0,81</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,26; 10,54</t>
+          <t>0,65; 10,09</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 3,81</t>
+          <t>-3,94; 4,04</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-7,18; 1,04</t>
+          <t>-7,0; 0,87</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,21; 11,64</t>
+          <t>2,87; 11,48</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,27; 6,89</t>
+          <t>0,24; 6,71</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 4,28</t>
+          <t>-2,21; 4,04</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,54; 29,36</t>
+          <t>6,9; 29,33</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,23; 1,9</t>
+          <t>-5,52; 1,94</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-9,7; -2,85</t>
+          <t>-9,49; -2,62</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 20,14</t>
+          <t>-1,87; 18,03</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 3,32</t>
+          <t>-1,42; 3,39</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,72; -0,15</t>
+          <t>-4,9; -0,04</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,87; 19,35</t>
+          <t>4,03; 19,65</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,71; 21,58</t>
+          <t>0,66; 20,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,86; 13,27</t>
+          <t>-6,22; 12,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19,03; 90,65</t>
+          <t>20,01; 87,99</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-11,15; 4,28</t>
+          <t>-11,79; 4,47</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-20,39; -6,58</t>
+          <t>-20,02; -6,1</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 46,4</t>
+          <t>-4,01; 41,82</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 8,6</t>
+          <t>-3,31; 8,99</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-11,57; -0,39</t>
+          <t>-11,95; -0,01</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,63; 49,79</t>
+          <t>10,08; 52,35</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-9,15; 3,35</t>
+          <t>-8,99; 3,43</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-12,37; -0,63</t>
+          <t>-13,09; -1,27</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,07; 15,63</t>
+          <t>3,82; 15,91</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-13,37; 0,36</t>
+          <t>-13,03; -0,31</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-16,72; -4,77</t>
+          <t>-17,02; -4,32</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-9,05; 1,95</t>
+          <t>-8,71; 2,19</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-8,79; 0,28</t>
+          <t>-8,68; 0,11</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-12,44; -4,07</t>
+          <t>-12,63; -4,31</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 7,7</t>
+          <t>-0,59; 7,54</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-25,68; 11,53</t>
+          <t>-25,73; 11,65</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-34,49; -1,04</t>
+          <t>-36,35; -3,62</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11,56; 53,37</t>
+          <t>10,41; 52,86</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-28,36; 1,01</t>
+          <t>-27,7; -0,44</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-35,31; -10,72</t>
+          <t>-35,72; -11,07</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-19,1; 4,78</t>
+          <t>-18,14; 5,43</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-22,01; 0,84</t>
+          <t>-21,98; 0,26</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-31,12; -11,41</t>
+          <t>-31,21; -11,88</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 21,87</t>
+          <t>-1,48; 21,05</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 3,99</t>
+          <t>-0,86; 4,03</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,08; -0,99</t>
+          <t>-5,73; -0,94</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,6; 19,14</t>
+          <t>2,71; 18,23</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,38; -0,28</t>
+          <t>-5,03; -0,13</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-11,88; -6,86</t>
+          <t>-11,57; -6,72</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-6,59; 5,38</t>
+          <t>-6,27; 5,0</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 1,01</t>
+          <t>-2,41; 1,0</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-8,16; -4,67</t>
+          <t>-8,24; -4,65</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 8,52</t>
+          <t>-1,09; 8,54</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 9,68</t>
+          <t>-1,95; 9,59</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-13,87; -2,34</t>
+          <t>-13,02; -2,27</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5,98; 46,25</t>
+          <t>6,04; 42,58</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-9,22; -0,5</t>
+          <t>-8,67; -0,23</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-20,33; -12,26</t>
+          <t>-19,87; -12,04</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-11,49; 9,46</t>
+          <t>-10,88; 8,81</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-4,73; 2,07</t>
+          <t>-4,77; 2,06</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-16,1; -9,43</t>
+          <t>-16,22; -9,59</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 17,04</t>
+          <t>-2,21; 17,11</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/PCS12_SP_R2-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/PCS12_SP_R2-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5,52</t>
+          <t>3,32</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,05</t>
+          <t>3,31</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>5,09</t>
+          <t>3,65</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 6,65</t>
+          <t>-2,12; 6,53</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,76; 3,88</t>
+          <t>-6,01; 3,53</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,5; 10,63</t>
+          <t>-1,73; 8,21</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,23; 1,49</t>
+          <t>-5,68; 1,05</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,67; 0,61</t>
+          <t>-6,69; 0,51</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,44; 7,39</t>
+          <t>-0,0; 6,62</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 2,76</t>
+          <t>-2,72; 2,74</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-4,98; 0,59</t>
+          <t>-5,05; 0,62</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,96; 7,84</t>
+          <t>0,95; 6,69</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>5,23%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 11,0</t>
+          <t>-3,32; 10,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-8,81; 6,44</t>
+          <t>-9,45; 5,85</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,8; 17,72</t>
+          <t>-2,69; 13,59</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,82; 2,01</t>
+          <t>-7,31; 1,41</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-8,75; 0,81</t>
+          <t>-8,69; 0,7</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,65; 10,09</t>
+          <t>-0,01; 8,95</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-3,94; 4,04</t>
+          <t>-3,8; 3,99</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-7,0; 0,87</t>
+          <t>-7,12; 0,9</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,87; 11,48</t>
+          <t>1,37; 9,78</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>14,19</t>
+          <t>7,76</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,86</t>
+          <t>1,39</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>9,7</t>
+          <t>4,73</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,24; 6,71</t>
+          <t>0,17; 6,75</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 4,04</t>
+          <t>-2,53; 3,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,9; 29,33</t>
+          <t>4,16; 10,89</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,52; 1,94</t>
+          <t>-4,87; 1,98</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-9,49; -2,62</t>
+          <t>-9,44; -2,53</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 18,03</t>
+          <t>-1,9; 4,52</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 3,39</t>
+          <t>-1,63; 3,36</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,9; -0,04</t>
+          <t>-4,77; -0,1</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,03; 19,65</t>
+          <t>2,39; 7,11</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>42,05%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>12,0%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,66; 20,73</t>
+          <t>0,62; 20,84</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,22; 12,76</t>
+          <t>-7,21; 12,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20,01; 87,99</t>
+          <t>11,8; 34,09</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-11,79; 4,47</t>
+          <t>-10,36; 4,49</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-20,02; -6,1</t>
+          <t>-20,09; -5,81</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 41,82</t>
+          <t>-4,03; 10,37</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 8,99</t>
+          <t>-4,01; 8,87</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-11,95; -0,01</t>
+          <t>-11,81; -0,25</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>10,08; 52,35</t>
+          <t>5,98; 18,69</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9,8</t>
+          <t>9,33</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-3,28</t>
+          <t>-2,37</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3,67</t>
+          <t>3,89</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-8,99; 3,43</t>
+          <t>-9,18; 2,45</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-13,09; -1,27</t>
+          <t>-13,5; -1,84</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,82; 15,91</t>
+          <t>3,5; 15,46</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-13,03; -0,31</t>
+          <t>-12,96; 0,66</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-17,02; -4,32</t>
+          <t>-17,79; -4,96</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-8,71; 2,19</t>
+          <t>-7,88; 3,16</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-8,68; 0,11</t>
+          <t>-9,25; 0,22</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-12,63; -4,31</t>
+          <t>-12,16; -3,98</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 7,54</t>
+          <t>-0,14; 8,05</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-7,44%</t>
+          <t>-5,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>10,26%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-25,73; 11,65</t>
+          <t>-26,19; 7,96</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-36,35; -3,62</t>
+          <t>-36,5; -5,36</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10,41; 52,86</t>
+          <t>8,93; 52,06</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-27,7; -0,44</t>
+          <t>-27,51; 1,66</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-35,72; -11,07</t>
+          <t>-37,03; -11,74</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-18,14; 5,43</t>
+          <t>-16,83; 7,68</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-21,98; 0,26</t>
+          <t>-22,95; 0,6</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-31,21; -11,88</t>
+          <t>-30,66; -11,19</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 21,05</t>
+          <t>-0,34; 22,71</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7,29</t>
+          <t>2,98</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-2,42</t>
+          <t>-4,18</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2,39</t>
+          <t>-0,61</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 4,03</t>
+          <t>-1,03; 3,83</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,73; -0,94</t>
+          <t>-5,97; -1,06</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,71; 18,23</t>
+          <t>0,41; 5,5</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,03; -0,13</t>
+          <t>-5,16; -0,44</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-11,57; -6,72</t>
+          <t>-11,7; -6,7</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-6,27; 5,0</t>
+          <t>-6,33; -2,03</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 1,0</t>
+          <t>-2,36; 0,96</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-8,24; -4,65</t>
+          <t>-8,08; -4,64</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 8,54</t>
+          <t>-2,35; 1,17</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-4,24%</t>
+          <t>-7,33%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>-1,22%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 9,59</t>
+          <t>-2,37; 9,31</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-13,02; -2,27</t>
+          <t>-13,6; -2,6</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6,04; 42,58</t>
+          <t>0,96; 13,42</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-8,67; -0,23</t>
+          <t>-8,85; -0,78</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-19,87; -12,04</t>
+          <t>-19,96; -11,93</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-10,88; 8,81</t>
+          <t>-10,85; -3,67</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-4,77; 2,06</t>
+          <t>-4,7; 1,92</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-16,22; -9,59</t>
+          <t>-15,85; -9,52</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 17,11</t>
+          <t>-4,59; 2,38</t>
         </is>
       </c>
     </row>
